--- a/sources/anna_step7.xlsx
+++ b/sources/anna_step7.xlsx
@@ -417,14 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA136"/>
+  <dimension ref="A1:AB134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="74" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -434,19 +434,20 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="115" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>49a03699-0f8f-478c-a122-9f813a04cb7e</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>f6ef61c9-44df-43c5-a67a-3a4c7b983802</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>5da9f55d-2858-4e06-a839-79d2d9665a9d</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>ec769e2a-e15f-47ab-8384-2ec26e9dd40f</t>
         </is>
@@ -730,22 +736,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uf+1+2 [~5]</t>
+          <t>uf+1+2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uf+1+2 [~5]</t>
+          <t>uf+1+2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Neck Throw [Tag]</t>
+          <t>Neck Throw</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neck Throw [Tag]</t>
+          <t>Neck Throw</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -790,10 +796,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
           <t>7b780836-e6a8-4d35-b8d8-1aaa5fecdccf</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>f6f59151-7f6f-4b5c-a55c-ed4b8f65c60a</t>
         </is>
@@ -855,12 +866,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>4d3512c5-c9ce-4277-a9db-d463e57ac63c</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>6cce2492-bb3d-478d-9492-8224efa29035</t>
         </is>
@@ -927,12 +938,12 @@
           <t>The throw attempt can also be blocked.</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>87bc0aac-5923-4796-9e8f-802e0bb1a21e</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>ec3730ad-c645-47e7-b98e-2092e993a4fb</t>
         </is>
@@ -989,12 +1000,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1051,12 +1062,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1113,12 +1124,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1250,20 +1261,25 @@
       </c>
       <c r="X13" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y13" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1345,12 +1361,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>593c8b38-d49a-417d-9a40-5207194a6ba2</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>cb815b0e-cebd-4558-a08b-9e3492bf6e56</t>
         </is>
@@ -1432,12 +1448,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>d117af8b-4761-4bd4-8ac9-f1ff8a1e0dae</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>45a9906f-7b37-467c-9929-b60ca268e7c1</t>
         </is>
@@ -1519,12 +1535,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>e0297502-ad23-4f43-b8c5-845d8f91a4e0</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>06933ec6-90d4-44e0-9c84-762e733a20e5</t>
         </is>
@@ -1606,12 +1622,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>f0ec242b-0d4c-4c83-abd5-cc8e63154c83</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>a7358778-24b7-4825-be19-7b7af3be3ada</t>
         </is>
@@ -1693,12 +1709,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>9ca9669d-3630-474c-bc74-b9bee809742d</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>37683fae-689f-465d-938a-a7e759372311</t>
         </is>
@@ -1780,12 +1796,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>d7c3d670-3a61-44f1-9fef-20199733eda2</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>3d66b2e5-d4ca-4493-985a-56b683434ded</t>
         </is>
@@ -1867,12 +1883,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>ca32c94d-9d90-4469-9611-30eef7659719</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>baa55fbf-f826-42da-ba7d-9eb30917f8b0</t>
         </is>
@@ -1954,12 +1970,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>3f88fc9b-5923-4864-a02f-cd0014bfc277</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>d0788a20-0899-45f5-89da-aaa19a62d3c2</t>
         </is>
@@ -2041,12 +2057,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>e5b89261-3185-417f-ae37-f70faaac9682</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>6eb60534-dfce-46a5-b56a-aa42284c7ff8</t>
         </is>
@@ -2128,12 +2144,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>f5dac5a7-1b8a-4e59-9e8e-40e90c82d2ad</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>7b42a1e2-b159-4aed-80f8-cf637fc22c88</t>
         </is>
@@ -2215,12 +2231,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>6b819028-93fe-4a98-a392-96ea8c468631</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>ee2320ab-89ad-4d27-b04b-16466a271572</t>
         </is>
@@ -2302,12 +2318,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>86a587ae-61c9-4a27-b319-22f3baf1a596</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>9ada57b5-f74b-4cbd-bdb0-28b67b01ac3c</t>
         </is>
@@ -2389,12 +2405,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>62257bf1-00a7-4829-9b3d-25d97eefe6d6</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>40175df6-a47c-438b-9cc2-4c412490a5b0</t>
         </is>
@@ -2476,12 +2492,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>9aef731c-5155-4f46-a01f-51dcb61e65de</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>9ede7b69-5e21-4ae0-8fe6-d62b887fdb0c</t>
         </is>
@@ -2563,12 +2579,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>59207b67-5f57-4cf7-a7d1-90c4272de645</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>76f3c0f1-2dad-4dd5-8702-fdf023a04a87</t>
         </is>
@@ -2650,12 +2666,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>28e75892-3b7d-416a-b1f3-368158f0fc6b</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>cd1ded75-7ea5-49fd-9b29-48b4c3c69872</t>
         </is>
@@ -2737,12 +2753,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>fe9d02ea-8837-4412-8fbc-f3a51ea2ef5d</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>669cf9d9-57eb-4793-bd4c-e2b5d72dbe17</t>
         </is>
@@ -2824,12 +2840,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>58a43e92-8306-4eb6-babc-37dcadbf71d8</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>ce71d0ec-d7ce-4abc-94c9-f5d4c9cfa4c9</t>
         </is>
@@ -2911,12 +2927,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>c8abafa3-b33c-48fb-8963-ceed5a66c1cd</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>0ffb5ed7-0a32-4e78-aa52-0dfe01d629e9</t>
         </is>
@@ -2998,12 +3014,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>6daddf42-e430-419b-977e-b57ccf081025</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>3171e7f3-e0c5-4743-95ed-1abf8405257b</t>
         </is>
@@ -3085,12 +3101,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>90573ac2-b100-43a2-919e-292ff7286ad8</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>6253c737-3b4d-418f-96ad-f3c554b2b9ba</t>
         </is>
@@ -3172,12 +3188,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>dbcb43cb-617b-43d6-bb6e-9bd3f8d3d643</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>64118522-d07d-46dc-8b17-fb3c8e178f88</t>
         </is>
@@ -3259,12 +3275,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>d96aacd6-8be0-449e-8b5d-e9045a0e109f</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>e69f6bc9-7046-4c71-ac4f-b59b5219ac28</t>
         </is>
@@ -3346,12 +3362,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>ab4da62a-3128-48cf-b7e6-6aa4555bba5e</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>29d98163-347e-4e6f-aa4d-d52829dfcb70</t>
         </is>
@@ -3483,20 +3499,25 @@
       </c>
       <c r="X40" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y40" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3505,12 +3526,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>df+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>df+1,2</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3525,22 +3546,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>+1 +1</t>
+          <t>+1 -5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3565,258 +3586,248 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>4,10</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>mh</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Low Kick</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>Double Punch – Low Kick</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>+1 -5</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>+1 -5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>+7 +7</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>+7 +7</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>+7 +7</t>
-        </is>
-      </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4,10</t>
+          <t>4,10,10</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
+          <t>hhl</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Does not work starting with d/f+1,2</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>74320b9b-6947-4250-be78-d728f6f0ae88</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BT 1,2</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BT 1,2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>BT 2,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Double Punch</t>
+          <t>– Bermuda Triangle</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Double Punch</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
+          <t>Double Punch – Bermuda Triangle</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>+1 -5 -19</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 KD</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 KD</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>15,10</t>
+          <t>4,10,15</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>hh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
+          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BT 1,2,3</t>
+          <t>1,2,1,4,2 [~U_~D]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>– Low Kick</t>
+          <t>– Snake [SS]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Double Punch – Low Kick</t>
+          <t>Double Punch – Snake [SS]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3824,91 +3835,101 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>+1 0 +2</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>-8 -5</t>
+          <t>+1 -5 +1 0 +2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 +12 -2 0</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>+12 -2 0</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>+3 +7</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6,15,12</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>15,10,10</t>
+          <t>4,10,6,15,12</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>hhl</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>hhhhh</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Does not work starting with d/f+1,2</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>fefdb095-541f-4d3e-939a-f3c64b7764d5</t>
+          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>c924ef1d-a211-4681-b97f-c72dcfadc034</t>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BT 1,2,4</t>
+          <t>1,2,1,4,2 [~U_~D],3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>– Bermuda Triangle</t>
+          <t>–– High Kick</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Double Punch – Bermuda Triangle</t>
+          <t>Double Punch – Snake [SS] – High Kick</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3918,47 +3939,47 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-8 -5 -19</t>
+          <t>+1 -5 +1 0 +2 0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+3 +7 KD</t>
+          <t>+7 +7 +12 -2 0 +9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>+3 +7 KD</t>
+          <t>+7 +7 +12 -2 0 +9</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>15,10,15</t>
+          <t>4,10,6,15,12,17</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3968,44 +3989,49 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>hhh</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>02cdaf34-b75f-4d9e-8eb0-6c4fa1d43d20</t>
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>7bdd8152-f754-413b-93c7-6a475498cf57</t>
+          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>–– uf+3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D]</t>
+          <t>1,2,1,4,2 [~U_~D],uf+3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>–– Bone Cutter</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS]</t>
+          <t>Double Punch – Snake [SS] – Bone Cutter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4013,39 +4039,24 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>+1 0 +2</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>+1 -5 +1 0 +2</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>+12 -2 0</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 -2 0</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>6,15,12</t>
+          <t>13,10,10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4055,59 +4066,54 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>15,10,6,15,12</t>
+          <t>4,10,6,15,12,13,10,10</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>hhhhh</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
+          <t>hhhhhh</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
         <is>
           <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>41065dfb-ba4e-41c9-a420-6d59ce98bf8e</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],3</t>
+          <t>1,2,1,4,2 [~U_~D],4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>–– High Kick</t>
+          <t>–– Spin Trip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
+          <t>Double Punch – Snake [SS] – Spin Trip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4117,75 +4123,75 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2 0</t>
+          <t>+1 -5 +1 0 +2 -23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 +9</t>
+          <t>+7 +7 +12 -2 0 KD</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 +9</t>
+          <t>+7 +7 +12 -2 0 KD</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,17</t>
+          <t>4,10,6,15,12,21</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>hhhhhh</t>
+          <t>hhhhhL</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>d0568b44-b953-4c64-af12-551ed65bde27</t>
+          <t>BS</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>e48f0a78-2da9-48e4-8d2d-3e422a9029c9</t>
+          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
+        <is>
+          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
         <is>
           <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
         </is>
@@ -4194,22 +4200,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>–– uf+3</t>
+          <t>– 1,b+4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],uf+3</t>
+          <t>1,2,1,b+4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>–– Bone Cutter</t>
+          <t>– Jab Rush - Low Kick</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+          <t>Double Punch – Jab Rush - Low Kick</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4217,81 +4223,106 @@
           <t>8</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>+1 -10</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2</t>
+          <t>+1 -5 +1 -10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 +1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>+12 +1</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0</t>
+          <t>+7 +7 +12 +1</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>13,10,10</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,13,10,10</t>
+          <t>4,10,6,8</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>hhhhhh</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>be54fc7b-95ac-42d4-b8b3-fcb452c8baa5</t>
+          <t>hhhl</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>07611425-29b3-41ef-8a3f-0717f290a07d</t>
+          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>d82ea142-ec71-429a-aebc-0b35ec9ce20f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>–– 4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BT 1,2,1,4,2 [~U_~D],4</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>–– Spin Trip</t>
+          <t>PDK Combo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
+          <t>PDK Combo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4301,201 +4332,196 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>-8 -5 +1 0 +2 -23</t>
+          <t>+1 -10</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>+3 +7 +12 -2 0 KD</t>
+          <t>+7 +1</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>15,10,6,15,12,21</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>hhhhhL</t>
+          <t>hl</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>BS</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>caa2d86d-5b50-4cdf-9692-4d547308f93b</t>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>166cad2e-2c08-4739-b7e4-1e2d60f6a73b</t>
+          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>68a6b41e-e87d-46fd-a7e1-f471e9ceb5c5</t>
+          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>– 1,b+4</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BT 1,2,1,b+4</t>
+          <t>df+1,2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>– Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Double Punch – Jab Rush - Low Kick</t>
+          <t>Double Punch</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>-8 -5 +1 -10</t>
+          <t>+1 +1</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+3 +7 +12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>+3 +7 +12 +1</t>
+          <t>+7 +7</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>15,10,6,8</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>hl</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>hhhl</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>1b40f311-91f7-4a46-be3b-81978d302f90</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>b301db8a-cbb4-4227-a630-d5ca1ba4fe0e</t>
+          <t>d0c5a7da-b497-4286-a857-fd8930564a52</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+          <t>38c084ac-b201-4176-b5c8-6332f4f011fb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT 1,2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>BT 1,2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BT 2,2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PDK Combo</t>
+          <t>Double Punch</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4510,72 +4536,67 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>+1 -10</t>
+          <t>-8 -5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>+7 +1</t>
+          <t>+3 +7</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>15,10</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>hl</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>hl</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>3db16d2c-f04e-40cb-a74c-ecbfde854d6d</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>eb2690e4-5fed-4120-8ae5-c870948f502d</t>
+          <t>2f8871a4-5b86-4d12-b379-301dfb545e64</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>88b77f98-207e-4a96-bf95-31b06c11f4ac</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4696,12 @@
           <t>Stun only if the last hit is a counter hit.</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>5ecc7f2d-5ff4-47fc-b53b-578dc82b4f08</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>bcb9ecf1-dd7e-4b4f-93d8-f390fe423498</t>
         </is>
@@ -4777,12 +4798,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>e6a3d811-d19b-4fdc-96d7-cf106588eab5</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>58fa750a-47f4-41ab-b86f-87d684c44d37</t>
         </is>
@@ -4864,12 +4885,12 @@
           <t>hhm</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>f3b84990-fc10-41b6-94e8-f2d90eae0851</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>c67d87ff-6d78-4ed9-bff6-135eec6bacae</t>
         </is>
@@ -4966,12 +4987,12 @@
           <t>JG CF</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>2ad2fac5-a9a4-4640-ab3c-504112adab53</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>e6e870aa-e934-480c-8fbd-f48459faa0a9</t>
         </is>
@@ -5068,12 +5089,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>ecde714c-2e4e-45bf-9b6d-7654c6fdcb54</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>70fca1cd-46e0-4c6b-9bcf-82266b9b25d2</t>
         </is>
@@ -5165,12 +5186,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>8f6850a0-15df-46d5-9f3d-1ec59a884c51</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>0bc2e63a-9cf2-43bc-bbff-93f094458bc8</t>
         </is>
@@ -5267,12 +5288,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>b4a57f33-a1b0-4d94-a800-ebd4572806b0</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>163928bc-8279-428c-9bd5-84541e8b2b65</t>
         </is>
@@ -5281,22 +5302,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SS+1+2 [~5]</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SS+1+2 [~5]</t>
+          <t>SS+1+2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bloody Chaos [Tag]</t>
+          <t>Bloody Chaos</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bloody Chaos [Tag]</t>
+          <t>Bloody Chaos</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5371,10 +5392,15 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
           <t>40c875c3-be26-4f05-943b-37ead8821247</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>9fee6283-1cbe-41fa-b37b-12de83c66bd0</t>
         </is>
@@ -5471,12 +5497,12 @@
           <t>JGc GB</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>9c3ec510-e425-4cd3-ba93-044ff757401d</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>d0008f7f-c481-4a33-9e4c-7e0b89b0b4ec</t>
         </is>
@@ -5573,12 +5599,12 @@
           <t>MS FCDc</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>f0033357-8c75-40fe-8d0f-c62c8a41dea7</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>0a057b35-6fa1-4112-bf93-a0bda112da9f</t>
         </is>
@@ -5670,12 +5696,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>9e4dd387-2d72-4044-8562-e1ee1ccfd27b</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>ce0776a5-0e21-49c0-8150-4f6f88b571a2</t>
         </is>
@@ -5772,12 +5798,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>f448e8b4-3163-4dd7-a142-23436e109977</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>6146c5da-f363-4202-932e-d6f1c320a738</t>
         </is>
@@ -5869,12 +5895,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>0d72716a-f576-42d4-a7ee-9f819ab12b71</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>fbf8b254-3e10-4d73-9387-6dad0b6b899e</t>
         </is>
@@ -5931,12 +5957,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>5fc33659-4816-42c2-adf4-8289099ba5ec</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>218b57e0-02e3-455f-94d7-bf802b4c685b</t>
         </is>
@@ -6033,12 +6059,12 @@
           <t>sm</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>727c03c1-d4ee-4af0-ad70-bde480ea4274</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>05c37aea-f6d8-4edb-9af8-cc5f5000d755</t>
         </is>
@@ -6140,12 +6166,12 @@
           <t>Auto Parries all high and mid attacks.</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>aaf095b1-8515-4804-b523-4bc573e912aa</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>0ee60c37-d7bb-49a3-a91a-9482a5cc89b0</t>
         </is>
@@ -6237,12 +6263,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>0f0eaaee-08ed-4e24-b7f2-6a4aa0933c34</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>81d73688-572e-422e-849f-524a6b4abc56</t>
         </is>
@@ -6299,12 +6325,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>cd8953b4-d2bb-4865-ae6e-1921b61ee3c4</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>043af910-429c-4871-85c4-e5ec9ba1eba5</t>
         </is>
@@ -6406,12 +6432,12 @@
           <t>JGc</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>8fdc5489-06cd-4fca-b5ba-e63e91150282</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>8677bf2a-9bed-43bd-9316-3d1524256971</t>
         </is>
@@ -6508,12 +6534,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>eb8070d4-f69c-42c4-af27-e53ded6fec2a</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>9dc97e75-2026-40bf-ba6d-514c44041836</t>
         </is>
@@ -6610,12 +6636,12 @@
           <t>JGc RC KS</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>7ddf4a3c-7631-47ec-9c6d-8d72cac36ebb</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>4c0ee3b2-7833-40c5-a9ff-7f63ddbeec9c</t>
         </is>
@@ -6707,12 +6733,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>2f8125dd-aefa-4244-8595-efa6be7eb169</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>28c3168c-2657-45b9-9eb7-2facd10a30fa</t>
         </is>
@@ -6804,12 +6830,12 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>4e4a9f92-dd5b-4bc2-a40e-e0ed6df3ffae</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>c286881b-7c1a-4ffb-bca4-65da2a40a310</t>
         </is>
@@ -6818,22 +6844,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>– 2 [~5]</t>
+          <t>– 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3,3,2 [~5]</t>
+          <t>3,3,2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>– Upper [Tag]</t>
+          <t>– Upper</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Spike Combo – Upper [Tag]</t>
+          <t>Spike Combo – Upper</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6903,15 +6929,20 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
           <t>48dc2f99-daf3-4e04-a9a2-4b0a1f4c5ea7</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>55884aab-d023-4704-aca0-901df358b4c7</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>4e4a9f92-dd5b-4bc2-a40e-e0ed6df3ffae</t>
         </is>
@@ -6998,17 +7029,17 @@
           <t>hlh</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>61e50243-a112-402c-b380-52b7a06f9f5a</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>c7837b2f-e6bb-497a-83a1-d9f34cf15a5c</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>4e4a9f92-dd5b-4bc2-a40e-e0ed6df3ffae</t>
         </is>
@@ -7017,27 +7048,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FC+3,2 [~5]</t>
+          <t>FC+3,2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FC+3,2 [~5]</t>
+          <t>FC+3,2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>d+3,2 [~5]</t>
+          <t>d+3,2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Low Spin Kick - Upper [Tag]</t>
+          <t>Low Spin Kick - Upper</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Low Spin Kick - Upper [Tag]</t>
+          <t>Low Spin Kick - Upper</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -7112,10 +7143,15 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
           <t>c72122fb-011b-4110-970d-2f3e2988615a</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>286b482b-2aba-4d20-8f18-794eff2d0865</t>
         </is>
@@ -7212,12 +7248,12 @@
           <t>Lh</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>1a12da17-0768-4ef8-90f3-f9f5d8c5dd8c</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>eb535eb5-011b-46fb-8c14-40618e2bd59f</t>
         </is>
@@ -7309,12 +7345,12 @@
           <t>Ll</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="Y79" t="inlineStr">
         <is>
           <t>7a3841ca-80d6-4b9a-bb27-26f020e6c6ca</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>4a0a86b4-e0c1-4278-8925-3e8a3d6b71f7</t>
         </is>
@@ -7406,12 +7442,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>d318c9d4-3b17-41c0-8086-fdc6c1a31d03</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>c75e2c66-2791-4f70-bf79-1710ecf5fc6e</t>
         </is>
@@ -7513,12 +7549,12 @@
           <t>Cannot be done after string SS cancels.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>2b42f71e-bd68-4c2f-a547-6285fa79e6f1</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>35a118c7-29bf-40a7-8afa-731ad7aa25bf</t>
         </is>
@@ -7610,12 +7646,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>6b60d24e-6f53-4b46-b4f1-4c924f126094</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>b06515c2-e447-4235-bd75-8a374401fffd</t>
         </is>
@@ -7707,17 +7743,17 @@
           <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>02266c87-12dd-41d3-879d-663dee145db8</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>ea741939-17be-4bd5-9405-c1fd5bd5932e</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>6b60d24e-6f53-4b46-b4f1-4c924f126094</t>
         </is>
@@ -7804,17 +7840,17 @@
           <t>mhhhh</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>deddb8f6-6e7d-4569-af97-bb8edfa3f0a2</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>8751226a-abf4-4605-af36-aaeb7921f843</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>02266c87-12dd-41d3-879d-663dee145db8</t>
         </is>
@@ -7886,17 +7922,17 @@
           <t>mhhhh</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>d00cd04f-30ce-4e91-9568-3693bae55ef0</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>8b44f70b-e086-4c83-965b-19b20bce66f9</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>02266c87-12dd-41d3-879d-663dee145db8</t>
         </is>
@@ -7988,17 +8024,17 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>f0541f18-6c40-476e-a706-42d2d04ca4a9</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>1f3e5e39-6f58-47d2-ad21-e3036369b4c1</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>02266c87-12dd-41d3-879d-663dee145db8</t>
         </is>
@@ -8085,17 +8121,17 @@
           <t>mhh</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>2f99966b-8c42-4b10-bcf1-0dfb509d0371</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>af12bd52-e4c9-4198-b6b5-fcabbe3e6a76</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>6b60d24e-6f53-4b46-b4f1-4c924f126094</t>
         </is>
@@ -8187,12 +8223,12 @@
           <t>mh</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>37690d6b-180b-44cf-ac43-3c4eadd6b614</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>fa8bb589-f4a9-41a6-bed3-ac25f9dc8523</t>
         </is>
@@ -8284,17 +8320,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>cb89825a-75f4-4d81-90ce-646cf767f96f</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>33ad9c39-b297-475f-9864-0628fcabfe10</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>37690d6b-180b-44cf-ac43-3c4eadd6b614</t>
         </is>
@@ -8386,17 +8422,17 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>c0031465-d619-483a-a52d-514ac7fad3aa</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>a2fd5632-2770-4233-a54e-587b925652ea</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>37690d6b-180b-44cf-ac43-3c4eadd6b614</t>
         </is>
@@ -8488,17 +8524,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>c64535d4-9ac6-4fc1-a0f4-2340b5e72c8b</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>2e5260fb-c5b0-437e-a6ff-4b00c92f1d09</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>37690d6b-180b-44cf-ac43-3c4eadd6b614</t>
         </is>
@@ -8585,17 +8621,17 @@
           <t>mhh</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>eb2fc591-080a-4ea0-bd50-f969133ade36</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>30359701-f1ba-4dd0-8b62-a85e31452540</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>37690d6b-180b-44cf-ac43-3c4eadd6b614</t>
         </is>
@@ -8647,12 +8683,12 @@
           <t>mhh</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>92cfc42c-cd44-4beb-92c5-29426ca1c073</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>08960b66-a959-46fa-8384-a6065d279200</t>
         </is>
@@ -8704,17 +8740,17 @@
           <t>mhhh</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>18499205-1b6e-437b-bbb2-040d67372770</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>9469a0e2-8483-451b-8789-7d9639c90d43</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>92cfc42c-cd44-4beb-92c5-29426ca1c073</t>
         </is>
@@ -8771,17 +8807,17 @@
           <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>d942c8fb-e8e1-4ae4-bdb6-38edab1b7d11</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>d68673f2-bd73-4eb1-9135-62a9eef46aa1</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>18499205-1b6e-437b-bbb2-040d67372770</t>
         </is>
@@ -8833,17 +8869,17 @@
           <t>mhhhhhh</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>35c5d9d8-7b68-45ea-8da7-4c5230a60ea2</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>5b10538b-1e97-4251-9f28-59515bbf166a</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>d942c8fb-e8e1-4ae4-bdb6-38edab1b7d11</t>
         </is>
@@ -8895,17 +8931,17 @@
           <t>mhhhhhh</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>e54a05d4-cb3d-457a-a155-90cbb407837d</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>52613306-e123-45b2-ab8f-efec20f86700</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>d942c8fb-e8e1-4ae4-bdb6-38edab1b7d11</t>
         </is>
@@ -8962,17 +8998,17 @@
           <t>BS</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>14cfc336-4cb4-4d36-8236-29a2ef120000</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>cac813f0-1cd5-426b-9c99-da6f2694e9c8</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>d942c8fb-e8e1-4ae4-bdb6-38edab1b7d11</t>
         </is>
@@ -9024,17 +9060,17 @@
           <t>mhhhh</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>e29b818d-b615-43c2-b431-3406282263a6</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>1ac6272f-2676-4d32-9edc-fdc8eb1a0144</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>18499205-1b6e-437b-bbb2-040d67372770</t>
         </is>
@@ -9086,17 +9122,17 @@
           <t>mhhh</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>799b10dc-0be0-4db3-bde1-696366edd9b8</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>7ff92877-370d-4d5d-8d17-1b8e71320d44</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>92cfc42c-cd44-4beb-92c5-29426ca1c073</t>
         </is>
@@ -9193,12 +9229,12 @@
           <t>L</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>755143bf-3e65-470c-87f8-216082c14ba1</t>
         </is>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Z101" t="inlineStr">
         <is>
           <t>307a59e3-ad41-4a03-81bd-f498f11194da</t>
         </is>
@@ -9295,12 +9331,12 @@
           <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
-      <c r="X102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>5a1a28e0-cd2d-4a6f-a14c-8a8ce7088ad1</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Z102" t="inlineStr">
         <is>
           <t>ca15e137-29c5-4ab6-9d0a-73bd8d4e7f87</t>
         </is>
@@ -9397,12 +9433,12 @@
           <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>ab9308ff-e068-4c15-b29c-1171421322ea</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Z103" t="inlineStr">
         <is>
           <t>db32b4d1-6b72-4669-8bb5-68450c0b741a</t>
         </is>
@@ -9499,12 +9535,12 @@
           <t>Side Step can be linked into Chaos Tail or Bloody Choas.</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>bbc2cf9a-42bd-4b05-93d8-4e31d4c0074c</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>05453269-209a-40f0-8259-3ab85c363322</t>
         </is>
@@ -9561,12 +9597,12 @@
           <t>Auto parries low attacks. Anna will reverse any throw attempt while in Cat Stance. Throw reversal does 25 damage.</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>b51fd1ce-80f3-4bad-8026-d4961bef5561</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>ad03788a-7500-430c-b26a-e84b28ddc0d0</t>
         </is>
@@ -9658,17 +9694,17 @@
           <t>SH GB</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>c0110b95-daa0-4f49-9781-30a84d1fdef5</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>093815ed-5ef6-4605-bdb9-463dcd4af06c</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>b51fd1ce-80f3-4bad-8026-d4961bef5561</t>
         </is>
@@ -9760,12 +9796,12 @@
           <t>hL</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>ed0864e2-b9b7-4536-be1d-8d3ff897579c</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>2b1666b9-b182-4811-83b3-13fe150c494e</t>
         </is>
@@ -9832,12 +9868,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>4852b84a-3991-4779-b0de-4784c3cfc043</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>f7056574-17e6-4742-900e-3e21afa42406</t>
         </is>
@@ -9846,27 +9882,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UB+4 [~5]</t>
+          <t>UB+4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>UB+4 [~5]</t>
+          <t>UB+4</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>U+4 [~5]; UF+4 [~5]</t>
+          <t>U+4; UF+4</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Flip Kick [Tag]</t>
+          <t>Flip Kick</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Flip Kick [Tag]</t>
+          <t>Flip Kick</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9946,10 +9982,15 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
           <t>44acb740-0fd7-4d85-9d85-2f2fd6c6845f</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>7f208ee7-52ff-482c-a3a1-dc5b2e50d88d</t>
         </is>
@@ -10046,12 +10087,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>92de2c5a-6fcb-47be-a573-ed0cfce15145</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>da801f88-25ab-48d1-b5af-6f2490e56101</t>
         </is>
@@ -10148,12 +10189,12 @@
           <t>KS</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="Y111" t="inlineStr">
         <is>
           <t>1728b322-23cb-4488-b4c1-8e4910002625</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>90dff98f-620d-4ff9-9f47-a7f5c556c020</t>
         </is>
@@ -10210,12 +10251,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>54989484-5005-4de1-baaf-5545d616f7a2</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>d8d1904d-cc16-48e3-9a05-7b6aee13eaaf</t>
         </is>
@@ -10347,20 +10388,25 @@
       </c>
       <c r="X115" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y115" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y115" s="1" t="inlineStr">
+      <c r="Z115" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z115" s="1" t="inlineStr">
+      <c r="AA115" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA115" s="1" t="inlineStr">
+      <c r="AB115" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10442,12 +10488,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>48b304a4-9ebc-400b-8d9a-c43a3b2ebc16</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>3deb1ec8-7a23-44a8-b631-88c6f0575098</t>
         </is>
@@ -10514,17 +10560,17 @@
           <t>!-</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>660bd864-ae47-4569-b962-ff40f8ccab32</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>128bac70-472d-4529-8667-03d8731c6f24</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
+      <c r="AA117" t="inlineStr">
         <is>
           <t>48b304a4-9ebc-400b-8d9a-c43a3b2ebc16</t>
         </is>
@@ -10606,12 +10652,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>a355c69a-0d37-41e0-9441-f9fe05322aa2</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>b8ba058c-b37e-4586-8ecc-b962264bfabe</t>
         </is>
@@ -10743,20 +10789,25 @@
       </c>
       <c r="X121" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y121" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y121" s="1" t="inlineStr">
+      <c r="Z121" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z121" s="1" t="inlineStr">
+      <c r="AA121" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA121" s="1" t="inlineStr">
+      <c r="AB121" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -10765,22 +10816,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5]</t>
+          <t>qcf+1+2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5]</t>
+          <t>qcf+1+2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag]</t>
+          <t>Palm Strike</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag]</t>
+          <t>Palm Strike</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10813,12 +10864,17 @@
           <t>Special Tag Throw with Nina only. Nina finishes with a Reverse Shoulder Lock. Total damage is 15,30.</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
         </is>
       </c>
-      <c r="AA122" t="inlineStr">
+      <c r="AB122" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10832,7 +10888,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],3,4,3,1+2</t>
+          <t>qcf+1+2,3,4,3,1+2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10842,7 +10898,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Arm Bar</t>
+          <t>Palm Strike – Arm Bar</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10865,17 +10921,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
+      <c r="AA123" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
         </is>
       </c>
-      <c r="AA123" t="inlineStr">
+      <c r="AB123" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10889,7 +10945,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1</t>
+          <t>qcf+1+2,1,3,2,1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10899,7 +10955,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock</t>
+          <t>Palm Strike – Standing Reverse Arm Lock</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10922,17 +10978,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="AA124" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AB124" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -10946,7 +11002,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1,2,1,3,4,1+2</t>
+          <t>qcf+1+2,1,3,2,1,2,1,3,4,1+2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10956,7 +11012,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock – Falling Reverse Arm Lock</t>
+          <t>Palm Strike – Standing Reverse Arm Lock – Falling Reverse Arm Lock</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10979,17 +11035,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
+      <c r="AA125" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
         </is>
       </c>
-      <c r="AA125" t="inlineStr">
+      <c r="AB125" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11003,7 +11059,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1,3,1,4,1+2,1+2</t>
+          <t>qcf+1+2,1,3,2,1,3,1,4,1+2,1+2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11013,7 +11069,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock – Rear Falcon Wing Squeeze</t>
+          <t>Palm Strike – Standing Reverse Arm Lock – Rear Falcon Wing Squeeze</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -11036,17 +11092,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
+      <c r="AA126" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
         </is>
       </c>
-      <c r="AA126" t="inlineStr">
+      <c r="AB126" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11060,7 +11116,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1,3,2,1,2,3,1+2,3+4,1+2</t>
+          <t>qcf+1+2,1,3,2,1,2,3,1+2,3+4,1+2</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11070,7 +11126,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Standing Reverse Arm Lock – Gatelatch Toss</t>
+          <t>Palm Strike – Standing Reverse Arm Lock – Gatelatch Toss</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -11093,17 +11149,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
         </is>
       </c>
-      <c r="AA127" t="inlineStr">
+      <c r="AB127" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11117,7 +11173,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1+3,4,1+2</t>
+          <t>qcf+1+2,1+3,4,1+2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11127,7 +11183,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Arm Sprain</t>
+          <t>Palm Strike – Arm Sprain</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -11150,17 +11206,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
         </is>
       </c>
-      <c r="AA128" t="inlineStr">
+      <c r="AB128" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11174,7 +11230,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1+3,4,1+2,4,3,4,3+4,1+2</t>
+          <t>qcf+1+2,1+3,4,1+2,4,3,4,3+4,1+2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11184,7 +11240,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Arm Sprain – Inverted Crucifix</t>
+          <t>Palm Strike – Arm Sprain – Inverted Crucifix</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -11207,17 +11263,17 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
+      <c r="AA129" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
         </is>
       </c>
-      <c r="AA129" t="inlineStr">
+      <c r="AB129" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11231,7 +11287,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>qcf+1+2 [~5],1+3,4,1+2,1+2,4,3,1+2,1+2,1+2</t>
+          <t>qcf+1+2,1+3,4,1+2,1+2,4,3,1+2,1+2,1+2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11241,7 +11297,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Palm Strike [Tag] – Arm Sprain – Rear Cross Lock</t>
+          <t>Palm Strike – Arm Sprain – Rear Cross Lock</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -11264,17 +11320,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
+      <c r="AA130" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
         </is>
       </c>
-      <c r="AA130" t="inlineStr">
+      <c r="AB130" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11406,20 +11462,25 @@
       </c>
       <c r="X133" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y133" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y133" s="1" t="inlineStr">
+      <c r="Z133" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z133" s="1" t="inlineStr">
+      <c r="AA133" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA133" s="1" t="inlineStr">
+      <c r="AB133" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -11461,111 +11522,12 @@
           <t>hhhhhlhhhh</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>df+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>df+1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>10,15,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>mhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>3868d410-2e89-48d9-953a-b6d47bab49c4</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>ML only</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>BT 1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>BT 1,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>2,2,1,2,3,3,2,1,2,4</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>15,10,6,6,7,9,6,6,6,30</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>hhhhhlhhhh</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>2f43bade-2f95-4531-9ea3-4cdbb2bdd0bd</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
+      <c r="AB134" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/anna_step7.xlsx
+++ b/sources/anna_step7.xlsx
@@ -425,7 +425,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="68" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -3812,22 +3812,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>– 1,4,2 [~U_~D]</t>
+          <t>– 1,4,2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D]</t>
+          <t>1,2,1,4,2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS]</t>
+          <t>Double Punch – Snake</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3919,7 +3924,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],3</t>
+          <t>1,2,1,4,2,3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3929,7 +3934,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – High Kick</t>
+          <t>Double Punch – Snake – High Kick</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4021,7 +4026,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],uf+3</t>
+          <t>1,2,1,4,2,uf+3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4031,7 +4036,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Bone Cutter</t>
+          <t>Double Punch – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4103,7 +4108,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1,2,1,4,2 [~U_~D],4</t>
+          <t>1,2,1,4,2,4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4113,7 +4118,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Double Punch – Snake [SS] – Spin Trip</t>
+          <t>Double Punch – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7660,22 +7665,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>– 4&lt;2 [~U_~D]</t>
+          <t>– 4&lt;2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D]</t>
+          <t>df+3,1,4&lt;2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>– Snake [SS]</t>
+          <t>– Snake</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS]</t>
+          <t>Assault – Snake</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7767,7 +7777,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],3</t>
+          <t>df+3,1,4&lt;2,3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7777,7 +7787,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – High Kick</t>
+          <t>Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -7864,7 +7874,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],uf+3</t>
+          <t>df+3,1,4&lt;2,uf+3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7874,7 +7884,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Bone Cutter</t>
+          <t>Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -7946,7 +7956,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>df+3,1,4&lt;2 [~U_~D],4</t>
+          <t>df+3,1,4&lt;2,4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7956,7 +7966,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Assault – Snake [SS] – Spin Trip</t>
+          <t>Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8140,22 +8150,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D]</t>
+          <t>df+3,2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS]</t>
+          <t>Creeping Snake</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -8242,7 +8257,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],1,4</t>
+          <t>df+3,2,1,4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -8252,7 +8267,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Biting Snake</t>
+          <t>Creeping Snake – Biting Snake</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8344,7 +8359,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],3</t>
+          <t>df+3,2,3</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -8354,7 +8369,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – High Kick</t>
+          <t>Creeping Snake – High Kick</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8446,7 +8461,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],d+3</t>
+          <t>df+3,2,d+3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8456,7 +8471,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Low Kick</t>
+          <t>Creeping Snake – Low Kick</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8548,7 +8563,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>df+3,2 [~U_~D],4</t>
+          <t>df+3,2,4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8558,7 +8573,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Creeping Snake [SS] – Roundhouse</t>
+          <t>Creeping Snake – Roundhouse</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8759,22 +8774,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>–– 4&lt;2 [~U_~D]</t>
+          <t>–– 4&lt;2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D]</t>
+          <t>df+3,3,3,1,4&lt;2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>–– Snake [SS]</t>
+          <t>–– Snake</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS]</t>
+          <t>Spike Combo – Assault – Snake</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8831,7 +8851,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],3</t>
+          <t>df+3,3,3,1,4&lt;2,3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8841,7 +8861,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – High Kick</t>
+          <t>Spike Combo – Assault – Snake – High Kick</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8893,7 +8913,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],uf+3</t>
+          <t>df+3,3,3,1,4&lt;2,uf+3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8903,7 +8923,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Bone Cutter</t>
+          <t>Spike Combo – Assault – Snake – Bone Cutter</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8955,7 +8975,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>df+3,3,3,1,4&lt;2 [~U_~D],4</t>
+          <t>df+3,3,3,1,4&lt;2,4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8965,7 +8985,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spike Combo – Assault – Snake [SS] – Spin Trip</t>
+          <t>Spike Combo – Assault – Snake – Spin Trip</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9243,22 +9263,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>uf+4,3,4 [~U_~D]</t>
+          <t>uf+4,3,4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Can Opener [SS]</t>
+          <t>Can Opener</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -9345,22 +9370,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>d+4&lt;1 [~U_~D]</t>
+          <t>d+4&lt;1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -9447,22 +9477,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FC+4,1 [~U_~D]</t>
+          <t>FC+4,1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shin Kick - Spin Punch [SS]</t>
+          <t>Shin Kick - Spin Punch</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>(~U)SS; (~D)SS</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">

--- a/sources/anna_step7.xlsx
+++ b/sources/anna_step7.xlsx
@@ -1000,6 +1000,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>d0af4541-7b9a-41bf-9ff0-5f2b5d4a1a13</t>
@@ -1062,6 +1067,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr">
         <is>
           <t>1bd5e4f8-ba3c-42b7-8668-d0aacd0a7412</t>
@@ -1122,6 +1132,11 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>31ad5619-ed1a-41f7-95e0-e44eadc9aed1</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -10904,6 +10919,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
+        </is>
+      </c>
       <c r="Z122" t="inlineStr">
         <is>
           <t>7e1ce62b-b055-489f-b2df-17938cd65470</t>
@@ -10956,6 +10976,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
+        </is>
+      </c>
       <c r="Z123" t="inlineStr">
         <is>
           <t>92a0e966-a546-45f7-81d9-9e04d25a558e</t>
@@ -11013,6 +11038,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
+        </is>
+      </c>
       <c r="Z124" t="inlineStr">
         <is>
           <t>487cce17-0598-43ae-841e-c8d65b03adc2</t>
@@ -11070,6 +11100,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
+        </is>
+      </c>
       <c r="Z125" t="inlineStr">
         <is>
           <t>01df9a40-ec1c-4c04-abdf-abf4bf803a6a</t>
@@ -11127,6 +11162,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
+        </is>
+      </c>
       <c r="Z126" t="inlineStr">
         <is>
           <t>cfdb48e8-266a-4483-8dbc-a23b48dbea40</t>
@@ -11184,6 +11224,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
+        </is>
+      </c>
       <c r="Z127" t="inlineStr">
         <is>
           <t>ace888c8-b086-4f5e-80f5-f2f0c5dffa97</t>
@@ -11241,6 +11286,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
+        </is>
+      </c>
       <c r="Z128" t="inlineStr">
         <is>
           <t>f933e84c-5e2d-4683-b1d5-a29155eeef0b</t>
@@ -11298,6 +11348,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>93714c88-336b-411f-b863-f65c2a39733a</t>
+        </is>
+      </c>
       <c r="Z129" t="inlineStr">
         <is>
           <t>93714c88-336b-411f-b863-f65c2a39733a</t>
@@ -11353,6 +11408,11 @@
       <c r="U130" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>0e938de5-6095-4002-9ade-581f69b50247</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
@@ -11555,6 +11615,11 @@
       <c r="S134" t="inlineStr">
         <is>
           <t>hhhhhlhhhh</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>d61c2d77-39a1-494e-8996-5a62586356a9</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
